--- a/Documents/SETK-tr-TR-F2H26-Translation Document(1).xlsx
+++ b/Documents/SETK-tr-TR-F2H26-Translation Document(1).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dilara.tek\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Adobe-Form-Builder-main\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73262D3E-34F9-4D03-8319-DB7333BE25E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77FD1DEC-16F4-4597-BE40-E95B318209C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1710" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Complete Translations" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="187">
   <si>
     <t>Translation</t>
   </si>
@@ -706,6 +706,12 @@
   </si>
   <si>
     <t>https://www.samsung.com/tr/unpacked/thank-you</t>
+  </si>
+  <si>
+    <t>Project Code</t>
+  </si>
+  <si>
+    <t>F2H26</t>
   </si>
 </sst>
 </file>
@@ -902,12 +908,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -917,20 +917,18 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1369,16 +1367,20 @@
     </row>
     <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="16"/>
-      <c r="B2"/>
-      <c r="C2" s="17"/>
+      <c r="B2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>186</v>
+      </c>
       <c r="D2" s="17"/>
     </row>
     <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8"/>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="28"/>
+      <c r="C3" s="33"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
@@ -1537,7 +1539,7 @@
       <c r="B18" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="28" t="s">
         <v>123</v>
       </c>
       <c r="D18" s="15"/>
@@ -1621,7 +1623,7 @@
       <c r="B25" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="27" t="s">
         <v>131</v>
       </c>
       <c r="D25" s="13"/>
@@ -1761,7 +1763,7 @@
       <c r="B38" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C38" s="30" t="s">
+      <c r="C38" s="28" t="s">
         <v>123</v>
       </c>
       <c r="D38" s="15"/>
@@ -1861,7 +1863,7 @@
       <c r="B47" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C47" s="30" t="s">
+      <c r="C47" s="28" t="s">
         <v>123</v>
       </c>
       <c r="D47" s="13"/>
@@ -1885,7 +1887,7 @@
       <c r="B49" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="C49" s="31" t="s">
+      <c r="C49" s="29" t="s">
         <v>157</v>
       </c>
       <c r="D49" s="13"/>
@@ -1994,7 +1996,7 @@
         <v>47</v>
       </c>
       <c r="C61" s="12"/>
-      <c r="D61" s="32" t="s">
+      <c r="D61" s="30" t="s">
         <v>165</v>
       </c>
     </row>
@@ -2163,7 +2165,7 @@
       <c r="B75" t="s">
         <v>29</v>
       </c>
-      <c r="C75" s="29" t="s">
+      <c r="C75" s="27" t="s">
         <v>170</v>
       </c>
       <c r="D75" s="13"/>
@@ -2187,7 +2189,7 @@
       <c r="B77" t="s">
         <v>105</v>
       </c>
-      <c r="C77" s="30" t="s">
+      <c r="C77" s="28" t="s">
         <v>175</v>
       </c>
       <c r="D77" s="13"/>
@@ -2211,7 +2213,7 @@
       <c r="B79" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C79" s="33" t="s">
+      <c r="C79" s="31" t="s">
         <v>178</v>
       </c>
       <c r="D79" s="13" t="s">
@@ -2237,7 +2239,7 @@
       <c r="B81" t="s">
         <v>108</v>
       </c>
-      <c r="C81" s="30" t="s">
+      <c r="C81" s="28" t="s">
         <v>180</v>
       </c>
       <c r="D81" s="13" t="s">
